--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aghedupl.sharepoint.com/sites/TIMES-PL-PSE/Shared Documents/General/MODELE/2026/AGR_wyizolowany/SubRES_TMPL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patir\Documents\Praca ESMlab\1. TIMES-PL-PSE\2026\2. AGR_model_wyizolowany\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="315" documentId="13_ncr:1_{1583D22A-86E1-43A8-9C47-AFAFBCCD8BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{508A3B01-7554-4C5F-BDFE-CDF6AC5BBF0E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3E49AE-830C-4B03-B13B-954008E7522B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="5550" windowWidth="23010" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_ELC" sheetId="4" r:id="rId1"/>
@@ -174,9 +174,6 @@
     <t>PRI_BIOG_AGR</t>
   </si>
   <si>
-    <t>REG1</t>
-  </si>
-  <si>
     <t>Share-I~0</t>
   </si>
   <si>
@@ -226,6 +223,9 @@
   </si>
   <si>
     <t>Biogas plant - dry crop residues</t>
+  </si>
+  <si>
+    <t>PL</t>
   </si>
 </sst>
 </file>
@@ -1113,7 +1113,7 @@
   <sheetData>
     <row r="1" spans="2:28" x14ac:dyDescent="0.2">
       <c r="G1" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="2:28" x14ac:dyDescent="0.2">
@@ -1216,22 +1216,22 @@
         <v>42</v>
       </c>
       <c r="Q4" s="44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R4" s="45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T4" s="10" t="s">
         <v>22</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="V4" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="W4" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="X4" s="11" t="s">
         <v>25</v>
@@ -1282,13 +1282,13 @@
         <v>22</v>
       </c>
       <c r="U5" s="18" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="V5" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="W5" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="X5" s="19" t="s">
         <v>25</v>
@@ -1332,13 +1332,13 @@
         <v>22</v>
       </c>
       <c r="U6" s="10" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="V6" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="W6" s="11" t="s">
         <v>60</v>
-      </c>
-      <c r="W6" s="11" t="s">
-        <v>61</v>
       </c>
       <c r="X6" s="11" t="s">
         <v>25</v>
@@ -1382,13 +1382,13 @@
         <v>22</v>
       </c>
       <c r="U7" s="18" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="V7" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="W7" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="X7" s="19" t="s">
         <v>25</v>
@@ -1432,13 +1432,13 @@
         <v>22</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="V8" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="X8" s="11" t="s">
         <v>25</v>
@@ -1482,13 +1482,13 @@
         <v>22</v>
       </c>
       <c r="U9" s="46" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="V9" s="47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="W9" s="46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="X9" s="47" t="s">
         <v>25</v>
@@ -1814,10 +1814,10 @@
         <v>42</v>
       </c>
       <c r="Q21" s="44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R21" s="45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.2">
@@ -2286,10 +2286,10 @@
         <v>42</v>
       </c>
       <c r="Q38" s="44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R38" s="45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.2">
@@ -2758,10 +2758,10 @@
         <v>42</v>
       </c>
       <c r="Q55" s="41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R55" s="42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.2">
@@ -3229,10 +3229,10 @@
         <v>42</v>
       </c>
       <c r="Q72" s="41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R72" s="42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.2">
@@ -3700,10 +3700,10 @@
         <v>42</v>
       </c>
       <c r="Q89" s="41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R89" s="42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.2">
@@ -4153,14 +4153,14 @@
         <v>2005</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G1" s="17"/>
       <c r="I1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" t="s">
         <v>47</v>
-      </c>
-      <c r="K1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -4418,7 +4418,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -4429,7 +4429,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -4626,15 +4626,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="16" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="d5167bf0dd55feede3e29f1a430471b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="24bde18039da748f015df48b5e1e3648" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
@@ -4877,6 +4868,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4889,14 +4889,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B140F9D-34E6-48A4-B2AC-8BFCDECC6FB1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21CDA050-ACB1-4757-A444-D5206E780B43}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4911,6 +4903,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B140F9D-34E6-48A4-B2AC-8BFCDECC6FB1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aghedupl.sharepoint.com/sites/TIMES-PL-PSE/Shared Documents/General/MODELE/2026/AGR_wyizolowany/SubRES_TMPL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_FAF298504B329A478CF5E05CD4D5B4368BA5D520" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09EEAB7A-68E7-4BA3-9A2E-83CE5C248522}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_FAF298504B329A478CF5E05CD4D5B4368BA5D520" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4239F1F-8564-4469-A8BA-9F9D13D1593A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_ELC" sheetId="4" r:id="rId1"/>
     <sheet name="Arkusz1" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -15193,7 +15192,7 @@
         <v>0.56995401124169653</v>
       </c>
       <c r="Q14" s="37">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="R14" s="34">
         <v>3</v>
@@ -15222,7 +15221,7 @@
         <v>0.56995401124169653</v>
       </c>
       <c r="Q15" s="55">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="R15" s="35">
         <v>3</v>
@@ -15251,7 +15250,7 @@
         <v>4.6964210526315791</v>
       </c>
       <c r="Q16" s="37">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="R16" s="34">
         <v>3</v>
@@ -15280,7 +15279,7 @@
         <v>0.63123938879456709</v>
       </c>
       <c r="Q17" s="55">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="R17" s="35">
         <v>3</v>
@@ -18185,6 +18184,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
@@ -18193,15 +18201,6 @@
     <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18448,23 +18447,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1207B16C-BB4A-448E-B2D4-28FE823961AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8B90172-B8FE-411D-8979-A052051C5368}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -18472,6 +18454,38 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1207B16C-BB4A-448E-B2D4-28FE823961AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AE3EC3A-44F1-4E87-B0FA-8B639597397F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AE3EC3A-44F1-4E87-B0FA-8B639597397F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>